--- a/Measurements.xlsx
+++ b/Measurements.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fionn\OneDrive\Documents\tudelft\MSc\Q4\Fieldwork\B_Module_Fieldwork\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83DDA8B-9009-461B-95EE-604CE5DBAB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07036E8F-FEF7-4242-BCB2-AA16D771A483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -81,12 +81,6 @@
     <t>S4 Covica</t>
   </si>
   <si>
-    <t>time (sec)</t>
-  </si>
-  <si>
-    <t>time (min)</t>
-  </si>
-  <si>
     <t>Time</t>
   </si>
   <si>
@@ -97,6 +91,12 @@
   </si>
   <si>
     <t>naming of test runs: Location_calcite type_grainsize_number of test                                example: LG_Lake_PC_GS250_3                     (lagunazo lake, pure calcite, grainsize 250 microns, test run number 3)</t>
+  </si>
+  <si>
+    <t>Time (min)</t>
+  </si>
+  <si>
+    <t>Time (sec)</t>
   </si>
 </sst>
 </file>
@@ -303,11 +303,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
@@ -324,13 +323,13 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -702,8 +701,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
-        <v>19</v>
+      <c r="A1" s="11" t="s">
+        <v>17</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -719,48 +718,48 @@
     </row>
     <row r="2" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="1:15" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="9"/>
-      <c r="C3" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="11"/>
-    </row>
-    <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="7"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="M4" s="4"/>
+      <c r="N4" s="4"/>
+      <c r="O4" s="6"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
@@ -771,18 +770,6 @@
         <v>0</v>
       </c>
       <c r="C5" s="2"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
@@ -793,18 +780,6 @@
         <v>0.5</v>
       </c>
       <c r="C6" s="2"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
@@ -815,18 +790,6 @@
         <v>1</v>
       </c>
       <c r="C7" s="2"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
@@ -838,18 +801,6 @@
         <v>1.5</v>
       </c>
       <c r="C8" s="2"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
@@ -861,18 +812,6 @@
         <v>2</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
@@ -884,18 +823,6 @@
         <v>2.5</v>
       </c>
       <c r="C10" s="2"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
@@ -907,18 +834,6 @@
         <v>3</v>
       </c>
       <c r="C11" s="2"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
@@ -930,18 +845,6 @@
         <v>3.5</v>
       </c>
       <c r="C12" s="2"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
@@ -953,18 +856,6 @@
         <v>4</v>
       </c>
       <c r="C13" s="2"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
@@ -976,18 +867,6 @@
         <v>4.5</v>
       </c>
       <c r="C14" s="2"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
@@ -999,18 +878,6 @@
         <v>5</v>
       </c>
       <c r="C15" s="2"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3"/>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="3"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
@@ -1022,20 +889,8 @@
         <v>5.5</v>
       </c>
       <c r="C16" s="2"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <f t="shared" si="1"/>
         <v>360</v>
@@ -1045,20 +900,8 @@
         <v>6</v>
       </c>
       <c r="C17" s="2"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3"/>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <f t="shared" si="1"/>
         <v>390</v>
@@ -1068,20 +911,8 @@
         <v>6.5</v>
       </c>
       <c r="C18" s="2"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <f t="shared" si="1"/>
         <v>420</v>
@@ -1091,20 +922,8 @@
         <v>7</v>
       </c>
       <c r="C19" s="2"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3"/>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <f t="shared" si="1"/>
         <v>450</v>
@@ -1114,20 +933,8 @@
         <v>7.5</v>
       </c>
       <c r="C20" s="2"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <f t="shared" si="1"/>
         <v>480</v>
@@ -1137,20 +944,8 @@
         <v>8</v>
       </c>
       <c r="C21" s="2"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3"/>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <f t="shared" si="1"/>
         <v>510</v>
@@ -1160,20 +955,8 @@
         <v>8.5</v>
       </c>
       <c r="C22" s="2"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
-      <c r="M22" s="3"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="3"/>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <f t="shared" si="1"/>
         <v>540</v>
@@ -1183,20 +966,8 @@
         <v>9</v>
       </c>
       <c r="C23" s="2"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="3"/>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <f t="shared" si="1"/>
         <v>570</v>
@@ -1206,20 +977,8 @@
         <v>9.5</v>
       </c>
       <c r="C24" s="2"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3"/>
-      <c r="M24" s="3"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>A24+30</f>
         <v>600</v>
@@ -1229,20 +988,8 @@
         <v>10</v>
       </c>
       <c r="C25" s="2"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="3"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26">
         <f t="shared" si="1"/>
         <v>630</v>
@@ -1252,20 +999,8 @@
         <v>10.5</v>
       </c>
       <c r="C26" s="2"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="3"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <f t="shared" si="1"/>
         <v>660</v>
@@ -1275,20 +1010,8 @@
         <v>11</v>
       </c>
       <c r="C27" s="2"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="3"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28">
         <f t="shared" si="1"/>
         <v>690</v>
@@ -1298,18 +1021,6 @@
         <v>11.5</v>
       </c>
       <c r="C28" s="2"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-      <c r="J28" s="3"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="3"/>
-      <c r="M28" s="3"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Measurements.xlsx
+++ b/Measurements.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fionn\OneDrive\Documents\tudelft\MSc\Q4\Fieldwork\B_Module_Fieldwork\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07036E8F-FEF7-4242-BCB2-AA16D771A483}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51987FF5-F454-4515-890D-412234F74073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pH values" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Tests" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/Measurements.xlsx
+++ b/Measurements.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10916"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fionn\OneDrive\Documents\tudelft\MSc\Q4\Fieldwork\B_Module_Fieldwork\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dunyaschotman/Documents/AES_Msc/Q1.4 Fieldwork/Fieldwork_lab/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51987FF5-F454-4515-890D-412234F74073}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF3884CC-6F3E-4A40-A2E6-A06F7418B439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="23260" windowHeight="12460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pH values" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>Location</t>
   </si>
@@ -97,6 +97,45 @@
   </si>
   <si>
     <t>Time (sec)</t>
+  </si>
+  <si>
+    <t>0.907</t>
+  </si>
+  <si>
+    <t>1.5</t>
+  </si>
+  <si>
+    <t>1.88</t>
+  </si>
+  <si>
+    <t>5.68</t>
+  </si>
+  <si>
+    <t>1.8</t>
+  </si>
+  <si>
+    <t>2.31</t>
+  </si>
+  <si>
+    <t>2.12</t>
+  </si>
+  <si>
+    <t>Oyster shell test in field</t>
+  </si>
+  <si>
+    <t>[18:57, 03-06-2026] +31 6 28228649: Oyster shell test (not crushed):</t>
+  </si>
+  <si>
+    <t>Start pH: 2.37</t>
+  </si>
+  <si>
+    <t>End pH after 5min: 2.37</t>
+  </si>
+  <si>
+    <t>[18:57, 03-06-2026] +31 6 28228649: Oyster shell test (crushed)</t>
+  </si>
+  <si>
+    <t>Start ph: 2.36</t>
   </si>
 </sst>
 </file>
@@ -303,7 +342,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -332,9 +371,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -612,18 +657,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="12.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.5546875" customWidth="1"/>
-    <col min="4" max="4" width="23.21875" customWidth="1"/>
+    <col min="3" max="3" width="16.5" customWidth="1"/>
+    <col min="4" max="4" width="23.1640625" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
     <col min="6" max="6" width="19.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.44140625" customWidth="1"/>
+    <col min="7" max="7" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -643,45 +688,185 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B2" s="14"/>
+      <c r="C2" s="14">
+        <v>2</v>
+      </c>
+      <c r="D2" s="15">
+        <v>2289</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="14"/>
+      <c r="C4" s="14">
+        <v>1</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B7" s="14"/>
+      <c r="C7" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B9" s="14"/>
+      <c r="C9" s="14">
+        <v>5</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B13" s="14"/>
+      <c r="C13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>13</v>
       </c>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B20" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B21" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B22" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B23" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B24" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B25" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -692,15 +877,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9B4780E-0916-405A-AA62-F9DCA1CC4D68}">
   <dimension ref="A1:O28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.21875" customWidth="1"/>
-    <col min="2" max="2" width="39.21875" customWidth="1"/>
+    <col min="1" max="1" width="19.1640625" customWidth="1"/>
+    <col min="2" max="2" width="39.1640625" customWidth="1"/>
     <col min="3" max="3" width="32.33203125" customWidth="1"/>
     <col min="4" max="4" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>17</v>
       </c>
@@ -716,8 +901,8 @@
       <c r="K1" s="12"/>
       <c r="L1" s="13"/>
     </row>
-    <row r="2" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="1:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:15" ht="19" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>14</v>
       </c>
@@ -738,7 +923,7 @@
       <c r="N3" s="8"/>
       <c r="O3" s="10"/>
     </row>
-    <row r="4" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>19</v>
       </c>
@@ -761,7 +946,7 @@
       <c r="N4" s="4"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>0</v>
       </c>
@@ -771,7 +956,7 @@
       </c>
       <c r="C5" s="2"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>30</v>
       </c>
@@ -781,7 +966,7 @@
       </c>
       <c r="C6" s="2"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>60</v>
       </c>
@@ -791,7 +976,7 @@
       </c>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8">
         <f>A7+30</f>
         <v>90</v>
@@ -802,7 +987,7 @@
       </c>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9">
         <f t="shared" ref="A9:A28" si="1">A8+30</f>
         <v>120</v>
@@ -813,7 +998,7 @@
       </c>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10">
         <f t="shared" si="1"/>
         <v>150</v>
@@ -824,7 +1009,7 @@
       </c>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11">
         <f t="shared" si="1"/>
         <v>180</v>
@@ -835,7 +1020,7 @@
       </c>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12">
         <f t="shared" si="1"/>
         <v>210</v>
@@ -846,7 +1031,7 @@
       </c>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13">
         <f t="shared" si="1"/>
         <v>240</v>
@@ -857,7 +1042,7 @@
       </c>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14">
         <f t="shared" si="1"/>
         <v>270</v>
@@ -868,7 +1053,7 @@
       </c>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15">
         <f t="shared" si="1"/>
         <v>300</v>
@@ -879,7 +1064,7 @@
       </c>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16">
         <f t="shared" si="1"/>
         <v>330</v>
@@ -890,7 +1075,7 @@
       </c>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17">
         <f t="shared" si="1"/>
         <v>360</v>
@@ -901,7 +1086,7 @@
       </c>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18">
         <f t="shared" si="1"/>
         <v>390</v>
@@ -912,7 +1097,7 @@
       </c>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19">
         <f t="shared" si="1"/>
         <v>420</v>
@@ -923,7 +1108,7 @@
       </c>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20">
         <f t="shared" si="1"/>
         <v>450</v>
@@ -934,7 +1119,7 @@
       </c>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21">
         <f t="shared" si="1"/>
         <v>480</v>
@@ -945,7 +1130,7 @@
       </c>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22">
         <f t="shared" si="1"/>
         <v>510</v>
@@ -956,7 +1141,7 @@
       </c>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23">
         <f t="shared" si="1"/>
         <v>540</v>
@@ -967,7 +1152,7 @@
       </c>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24">
         <f t="shared" si="1"/>
         <v>570</v>
@@ -978,7 +1163,7 @@
       </c>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25">
         <f>A24+30</f>
         <v>600</v>
@@ -989,7 +1174,7 @@
       </c>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26">
         <f t="shared" si="1"/>
         <v>630</v>
@@ -1000,7 +1185,7 @@
       </c>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27">
         <f t="shared" si="1"/>
         <v>660</v>
@@ -1011,7 +1196,7 @@
       </c>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28">
         <f t="shared" si="1"/>
         <v>690</v>
